--- a/MyJob/Phan Thành Công - ĐÁNH GIÁ 2 THÁNG THỬ VIỆC.xlsx
+++ b/MyJob/Phan Thành Công - ĐÁNH GIÁ 2 THÁNG THỬ VIỆC.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -244,6 +244,34 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,22 +683,22 @@
       <c r="Z4" s="2" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="31">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>Họ và tên nhân viên:</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Phan Thành Công</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Quản lý trực tiếp: </t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Trần Đại Đồng</t>
         </is>
@@ -699,22 +727,22 @@
       <c r="Z5" s="8" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="31">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>Vị trí công việc:</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Thời gian thử việc/cộng tác viên từ: </t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
@@ -743,22 +771,22 @@
       <c r="Z6" s="8" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="31">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>Bộ phận:</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>Công nghệ thông tin</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày đánh giá: </t>
         </is>
       </c>
-      <c r="D7" s="0" t="n"/>
+      <c r="D7" s="44" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="7" t="n"/>
@@ -918,7 +946,7 @@
       <c r="Y11" s="8" t="n"/>
       <c r="Z11" s="8" t="n"/>
     </row>
-    <row r="12" ht="95" customHeight="1" s="31">
+    <row r="12" ht="70" customHeight="1" s="31">
       <c r="A12" s="32" t="n">
         <v>1</v>
       </c>
@@ -964,7 +992,7 @@
       <c r="Y12" s="8" t="n"/>
       <c r="Z12" s="8" t="n"/>
     </row>
-    <row r="13" ht="95" customHeight="1" s="31">
+    <row r="13" ht="70" customHeight="1" s="31">
       <c r="A13" s="32" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1038,7 @@
       <c r="Y13" s="8" t="n"/>
       <c r="Z13" s="8" t="n"/>
     </row>
-    <row r="14" ht="95" customHeight="1" s="31">
+    <row r="14" ht="116.5" customHeight="1" s="31">
       <c r="A14" s="32" t="n">
         <v>3</v>
       </c>
@@ -1056,7 +1084,7 @@
       <c r="Y14" s="8" t="n"/>
       <c r="Z14" s="8" t="n"/>
     </row>
-    <row r="15" ht="95" customHeight="1" s="31">
+    <row r="15" ht="54.5" customHeight="1" s="31">
       <c r="A15" s="38" t="n">
         <v>4</v>
       </c>
@@ -1102,16 +1130,16 @@
       <c r="Y15" s="8" t="n"/>
       <c r="Z15" s="8" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1" s="31">
-      <c r="A16" s="39" t="inlineStr">
+    <row r="16" ht="39" customHeight="1" s="31">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Tổng kết tự đánh giá về hoàn thành mục tiêu: Hoàn thành tốt các mục tiêu chính (khoảng 85-90%). Luồng công nợ end-to-end và tính cước tự động GWS Standard/Flex đã nghiệm thu; phần tính cước các dịch vụ còn lại (AWS, GCP...) đang tiếp tục theo lộ trình.</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -1194,18 +1222,21 @@
       <c r="Y18" s="2" t="n"/>
       <c r="Z18" s="2" t="n"/>
     </row>
-    <row r="19" ht="75" customHeight="1" s="31">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="19" ht="70" customHeight="1" s="31">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Những điểm bạn hài lòng nhất về hiệu quả công việc và đóng góp của mình trong thời gian qua?
 </t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Tinh thần chủ động và khả năng bao quát nhiều vai trò. Ngay giai đoạn đầu em đã chủ động xin phụ dev giao diện và OT để cứu deadline dự án web nội bộ. Ở module Công nợ, nhờ nền tảng lập trình, em không chỉ làm phân tích nghiệp vụ (BA) mà còn kiểm soát chất lượng code output và tham gia kiểm thử — giúp module về đích và nghiệm thu thành công.</t>
         </is>
       </c>
+      <c r="E19" s="47" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
@@ -1256,18 +1287,21 @@
       <c r="Y20" s="8" t="n"/>
       <c r="Z20" s="8" t="n"/>
     </row>
-    <row r="21" ht="75" customHeight="1" s="31">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="21" ht="85.5" customHeight="1" s="31">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Những khó khăn, thách thức bạn đã gặp phải và cách bạn đã vượt qua (hoặc chưa vượt qua)?
 </t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>Quy trình thu hồi công nợ của 5 dịch vụ cloud rất rối và chưa chuẩn hoá; đồng thời có giai đoạn PM đi công tác, việc triển khai chủ yếu qua AI nên rủi ro sai sót cao, và một sprint bị trễ do phạm vi phình to. Em vượt qua bằng cách: dành 1 tuần bóc tách toàn bộ quy trình thành tài liệu chuẩn, trực tiếp review lại code output nhờ background dev, và tập trung kiểm thử kỹ trước nghiệm thu. Kết quả: luồng công nợ đã chạy và nghiệm thu.</t>
         </is>
       </c>
+      <c r="E21" s="47" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
@@ -1318,18 +1352,21 @@
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="8" t="n"/>
     </row>
-    <row r="23" ht="75" customHeight="1" s="31">
-      <c r="A23" s="22" t="inlineStr">
+    <row r="23" ht="39" customHeight="1" s="31">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Bạn tự đánh giá mức độ hoàn thành tổng thể công việc được giao:
 </t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="B23" s="47" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>Hoàn thành tốt các mục tiêu chính (khoảng 85-90%). Luồng công nợ end-to-end và tính cước tự động GWS Standard/Flex đã nghiệm thu; phần tính cước các dịch vụ còn lại (AWS, GCP...) đang tiếp tục theo lộ trình.</t>
         </is>
       </c>
+      <c r="E23" s="47" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
@@ -1380,18 +1417,21 @@
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="8" t="n"/>
     </row>
-    <row r="25" ht="75" customHeight="1" s="31">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="25" ht="54.5" customHeight="1" s="31">
+      <c r="A25" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Bạn nhận thấy mình cần cải thiện những kỹ năng/kiến thức nào để làm tốt hơn công việc này?
 </t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="B25" s="47" t="n"/>
+      <c r="C25" s="47" t="n"/>
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>Kỹ năng ước lượng và kiểm soát phạm vi công việc (scope) để tránh trễ sprint; kiến thức sâu hơn về cơ chế billing của từng nền tảng cloud (đặc biệt GCP/AWS); và kỹ năng viết tài liệu đặc tả súc tích hơn để tăng tốc bàn giao.</t>
         </is>
       </c>
+      <c r="E25" s="47" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
@@ -1442,18 +1482,21 @@
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
     </row>
-    <row r="27" ht="75" customHeight="1" s="31">
-      <c r="A27" s="22" t="inlineStr">
+    <row r="27" ht="39" customHeight="1" s="31">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Bạn đánh giá mức độ hòa nhập với đội ngũ và văn hóa CloudAZ như thế nào?
 </t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Hoà nhập tốt. Em phối hợp cởi mở với team BA và dev, sẵn sàng hỗ trợ xuyên vai trò (nhận phụ dev, review code, kiểm thử). Tinh thần chủ động và cầu thị của em phù hợp với môi trường CloudAZ.</t>
         </is>
       </c>
+      <c r="E27" s="47" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
@@ -1504,18 +1547,20 @@
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
     </row>
-    <row r="29" ht="75" customHeight="1" s="31">
-      <c r="A29" s="23" t="inlineStr">
+    <row r="29" ht="54.5" customHeight="1" s="31">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>Ý kiến/Đề xuất khác (nếu có)?</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="B29" s="47" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>Em mong muốn được gắn bó lâu dài và chuyển sang hợp đồng chính thức để tiếp tục hoàn thiện module Công nợ cùng các phần tiếp theo của ERP. Em cũng mong nhận được phản hồi định hướng phát triển để làm tốt hơn.</t>
         </is>
       </c>
-      <c r="E29" s="8" t="n"/>
+      <c r="E29" s="45" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
